--- a/Result/profitability/1456.xlsx
+++ b/Result/profitability/1456.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.55</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6924999999999999</v>
+        <v>0.6324999999999998</v>
       </c>
       <c r="N2" t="n">
-        <v>33.83125</v>
+        <v>35.5125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.83</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8162499999999998</v>
+        <v>0.4649999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>30.84875</v>
+        <v>32.0525</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.77</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4487499999999999</v>
+        <v>0.4287499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>26.17125</v>
+        <v>27.04</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.78</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4112499999999998</v>
+        <v>0.3412499999999998</v>
       </c>
       <c r="N5" t="n">
-        <v>21.035</v>
+        <v>22.73</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.55</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3524999999999999</v>
+        <v>0.3149999999999998</v>
       </c>
       <c r="N6" t="n">
-        <v>16.63125</v>
+        <v>17.45625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.43</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3412499999999998</v>
+        <v>-0.2775000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>12.35</v>
+        <v>12.30375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.2</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2225000000000001</v>
+        <v>-0.2487500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>7.0825</v>
+        <v>7.9175</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1456</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>149</v>
+      </c>
+      <c r="D75" t="n">
+        <v>80</v>
+      </c>
+      <c r="E75" t="n">
+        <v>69</v>
+      </c>
+      <c r="F75" t="n">
+        <v>46.36</v>
+      </c>
+      <c r="G75" t="n">
+        <v>46</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>30.87%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-105</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-59</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-60</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.5437499999999998</v>
+      </c>
+      <c r="N75" t="n">
+        <v>39.2975</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.4883720930232558</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1683467741935485</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.4134146341463416</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
